--- a/outputs/client-preview/NeuraFlow_Product_Opportunity_Evidence_Illustrative_2026-08-15.xlsx
+++ b/outputs/client-preview/NeuraFlow_Product_Opportunity_Evidence_Illustrative_2026-08-15.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>Persistent advertiser activity, an Amazon movers placement and a clear search increase support a strong first-week entry.</t>
+          <t>Persistent advertiser activity, an Amazon bestseller placement and a clear search increase support a strong first-week entry.</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="U8" s="37" t="inlineStr">
         <is>
-          <t>Movers &amp; Shakers</t>
+          <t>Bestseller</t>
         </is>
       </c>
       <c r="V8" s="37" t="inlineStr">
